--- a/salidas/empresas/ADBE.xlsx
+++ b/salidas/empresas/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1286,7 +1298,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1311,7 +1323,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1361,7 +1373,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1386,7 +1398,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1411,7 +1423,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1436,7 +1448,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1461,7 +1473,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1486,7 +1498,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1511,7 +1523,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1536,7 +1548,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1561,7 +1573,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1586,7 +1598,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1611,7 +1623,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1636,7 +1648,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1661,7 +1673,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1711,7 +1723,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1736,7 +1748,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1765,7 +1777,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1794,7 +1806,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1823,7 +1835,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1852,7 +1864,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1881,7 +1893,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1910,7 +1922,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1939,7 +1951,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1968,7 +1980,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1997,7 +2009,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2026,7 +2038,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2055,7 +2067,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2113,7 +2125,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2142,7 +2154,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2171,7 +2183,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2200,7 +2212,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2229,7 +2241,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2258,7 +2270,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2287,7 +2299,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2316,7 +2328,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2345,7 +2357,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2374,7 +2386,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2403,7 +2415,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2432,7 +2444,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2461,7 +2473,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2490,7 +2502,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2548,7 +2560,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2606,7 +2618,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2635,7 +2647,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2664,7 +2676,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2693,7 +2705,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2722,7 +2734,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2751,7 +2763,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2780,7 +2792,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2809,7 +2821,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2838,7 +2850,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2867,7 +2879,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2896,7 +2908,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2925,7 +2937,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2954,7 +2966,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2983,7 +2995,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3012,7 +3024,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3041,7 +3053,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3099,7 +3111,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3128,7 +3140,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3157,7 +3169,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3186,7 +3198,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3215,7 +3227,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3244,7 +3256,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3273,7 +3285,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3302,7 +3314,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3331,7 +3343,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3360,7 +3372,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3389,7 +3401,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3418,7 +3430,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3447,7 +3459,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3476,7 +3488,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3505,7 +3517,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3534,7 +3546,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3592,7 +3604,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3621,7 +3633,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3650,7 +3662,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3679,7 +3691,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3708,7 +3720,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3737,7 +3749,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3766,7 +3778,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3795,7 +3807,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3824,7 +3836,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3853,7 +3865,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3911,7 +3923,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3940,7 +3952,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3969,7 +3981,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3998,7 +4010,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4027,7 +4039,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4085,7 +4097,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4114,7 +4126,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4143,7 +4155,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4201,7 +4213,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4230,7 +4242,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4259,7 +4271,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4288,7 +4300,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4317,7 +4329,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4346,7 +4358,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4375,7 +4387,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4404,7 +4416,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4433,7 +4445,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4462,7 +4474,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4491,7 +4503,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4520,7 +4532,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4578,7 +4590,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4607,7 +4619,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4636,7 +4648,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4665,7 +4677,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4694,7 +4706,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4723,7 +4735,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4752,7 +4764,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4781,7 +4793,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4810,7 +4822,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4839,7 +4851,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4868,7 +4880,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4897,7 +4909,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4926,7 +4938,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4955,7 +4967,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4984,7 +4996,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5013,7 +5025,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5042,7 +5054,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5071,7 +5083,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5100,7 +5112,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5158,7 +5170,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5187,7 +5199,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5216,7 +5228,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5274,7 +5286,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5303,7 +5315,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5332,7 +5344,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5361,7 +5373,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5390,7 +5402,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5419,7 +5431,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5448,7 +5460,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5477,7 +5489,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5506,7 +5518,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5535,7 +5547,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5564,7 +5576,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5593,7 +5605,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5622,7 +5634,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5651,7 +5663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5680,7 +5692,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5709,7 +5721,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5738,7 +5750,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5767,7 +5779,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5796,7 +5808,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5825,7 +5837,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5854,7 +5866,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5883,7 +5895,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5912,7 +5924,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5941,7 +5953,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5970,7 +5982,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5999,7 +6011,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6028,7 +6040,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6057,7 +6069,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6086,7 +6098,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6115,7 +6127,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6144,7 +6156,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6173,7 +6185,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6202,7 +6214,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6231,7 +6243,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6260,7 +6272,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6289,7 +6301,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6318,7 +6330,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6347,7 +6359,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6376,7 +6388,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6405,7 +6417,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6434,7 +6446,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6463,7 +6475,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6492,7 +6504,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6521,7 +6533,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6550,7 +6562,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6637,7 +6649,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6666,7 +6678,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6753,7 +6765,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6811,7 +6823,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6869,7 +6881,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7043,7 +7055,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7130,7 +7142,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7159,7 +7171,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7188,32 +7200,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>240.6900024414062</v>
+        <v>238.9299926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>240.6900024414062</v>
+        <v>238.9299926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>96093800</v>
+        <v>99767500</v>
       </c>
       <c r="E250" t="n">
         <v>17.91</v>
       </c>
       <c r="F250" t="n">
-        <v>13.43886110783954</v>
+        <v>13.34059143918377</v>
       </c>
       <c r="G250" t="n">
         <v>389200000</v>
       </c>
       <c r="H250" t="n">
-        <v>93676548950.19531</v>
+        <v>92991553149.41406</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2469008221993834</v>
+        <v>0.256339928057554</v>
       </c>
     </row>
   </sheetData>
@@ -7245,75 +7257,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39507</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39598</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39990</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7349,13 +7361,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39599</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39689</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7391,13 +7403,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39781</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39871</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40277</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7433,13 +7445,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39871</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39962</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>39990</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7475,13 +7487,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39963</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40053</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7517,13 +7529,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40054</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40144</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I7" t="n">
         <v>0.74</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K7" t="n">
@@ -7563,13 +7575,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40145</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40242</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40277</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7596,7 +7608,7 @@
       <c r="I8" t="n">
         <v>0.6799999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K8" t="n">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40243</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40333</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40361</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I9" t="n">
         <v>0.72</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K9" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40334</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40424</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40459</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I10" t="n">
         <v>0.9</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K10" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40425</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40515</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I11" t="n">
         <v>1.49</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K11" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40516</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40606</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40641</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I12" t="n">
         <v>1.71</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40641</v>
       </c>
       <c r="K12" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40607</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40697</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40723</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I13" t="n">
         <v>1.88</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40723</v>
       </c>
       <c r="K13" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40698</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40788</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40823</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I14" t="n">
         <v>1.83</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40823</v>
       </c>
       <c r="K14" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40789</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40879</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I15" t="n">
         <v>1.65</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="K15" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40880</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40970</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40998</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I16" t="n">
         <v>1.56</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40998</v>
       </c>
       <c r="K16" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40971</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41087</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I17" t="n">
         <v>1.56</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41087</v>
       </c>
       <c r="K17" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41062</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41179</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I18" t="n">
         <v>1.57</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41179</v>
       </c>
       <c r="K18" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41296</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I19" t="n">
         <v>1.66</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41296</v>
       </c>
       <c r="K19" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I20" t="n">
         <v>1.42</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="K20" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41335</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I21" t="n">
         <v>1.12</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="K21" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41516</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41550</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I22" t="n">
         <v>0.8799999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41550</v>
       </c>
       <c r="K22" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41607</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41660</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I23" t="n">
         <v>0.5700000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41660</v>
       </c>
       <c r="K23" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41726</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I24" t="n">
         <v>0.53</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41726</v>
       </c>
       <c r="K24" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41789</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41815</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I25" t="n">
         <v>0.55</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41815</v>
       </c>
       <c r="K25" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41880</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41907</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I26" t="n">
         <v>0.48</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41907</v>
       </c>
       <c r="K26" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41881</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41971</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42024</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I27" t="n">
         <v>0.52</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42024</v>
       </c>
       <c r="K27" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41972</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42062</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42088</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I28" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42088</v>
       </c>
       <c r="K28" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42153</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42179</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I29" t="n">
         <v>0.72</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42179</v>
       </c>
       <c r="K29" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42154</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42244</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I30" t="n">
         <v>0.97</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="K30" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42245</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42335</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42388</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I31" t="n">
         <v>1.24</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42388</v>
       </c>
       <c r="K31" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42336</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42433</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I32" t="n">
         <v>1.57</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="K32" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42434</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42524</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42550</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I33" t="n">
         <v>1.76</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42550</v>
       </c>
       <c r="K33" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42525</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42615</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42640</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I34" t="n">
         <v>1.96</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42640</v>
       </c>
       <c r="K34" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42616</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42706</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I35" t="n">
         <v>2.32</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="K35" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42707</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42797</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42823</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I36" t="n">
         <v>2.62</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42823</v>
       </c>
       <c r="K36" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42798</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42888</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42914</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I37" t="n">
         <v>2.89</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42914</v>
       </c>
       <c r="K37" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42889</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43005</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I38" t="n">
         <v>3.19</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43005</v>
       </c>
       <c r="K38" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42980</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43122</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I39" t="n">
         <v>3.39</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43122</v>
       </c>
       <c r="K39" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43071</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43161</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43187</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I40" t="n">
         <v>3.76</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43187</v>
       </c>
       <c r="K40" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43162</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43278</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I41" t="n">
         <v>4.34</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43278</v>
       </c>
       <c r="K41" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43253</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43369</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I42" t="n">
         <v>4.84</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43369</v>
       </c>
       <c r="K42" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I43" t="n">
         <v>5.21</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="K43" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43551</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I44" t="n">
         <v>5.4</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43551</v>
       </c>
       <c r="K44" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43526</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I45" t="n">
         <v>5.36</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="K45" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43707</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43734</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I46" t="n">
         <v>5.630000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43734</v>
       </c>
       <c r="K46" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43798</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43851</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I47" t="n">
         <v>6</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43851</v>
       </c>
       <c r="K47" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43889</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I48" t="n">
         <v>6.6</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="K48" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43980</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44006</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I49" t="n">
         <v>7.58</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44006</v>
       </c>
       <c r="K49" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43981</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44071</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I50" t="n">
         <v>7.94</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="K50" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44072</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44162</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I51" t="n">
         <v>10.84</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="K51" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44163</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44260</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I52" t="n">
         <v>11.49</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K52" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44261</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44351</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I53" t="n">
         <v>11.54</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K53" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44352</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44442</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44468</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I54" t="n">
         <v>12.09</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44468</v>
       </c>
       <c r="K54" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44443</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44533</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I55" t="n">
         <v>10.02</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="K55" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44534</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44624</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I56" t="n">
         <v>10.07</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="K56" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44625</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44715</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44741</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I57" t="n">
         <v>10.24</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44741</v>
       </c>
       <c r="K57" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44716</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44806</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44832</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I58" t="n">
         <v>10.14</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44832</v>
       </c>
       <c r="K58" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44807</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44897</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44943</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I59" t="n">
         <v>10.1</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44943</v>
       </c>
       <c r="K59" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44898</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44988</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I60" t="n">
         <v>10.15</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="K60" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44989</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45079</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I61" t="n">
         <v>10.48</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="K61" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45080</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45196</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I62" t="n">
         <v>11.11</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45196</v>
       </c>
       <c r="K62" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45171</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I63" t="n">
         <v>11.82</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="K63" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45262</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45378</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I64" t="n">
         <v>10.47</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45378</v>
       </c>
       <c r="K64" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45353</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I65" t="n">
         <v>11.14</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="K65" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45534</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I66" t="n">
         <v>11.85</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="K66" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45625</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I67" t="n">
         <v>12.36</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="K67" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I68" t="n">
         <v>15.14</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="K68" t="n">
@@ -10369,13 +10381,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45717</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45807</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="I69" t="n">
         <v>15.59</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="K69" t="n">
@@ -10415,13 +10427,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10448,7 +10460,7 @@
       <c r="I70" t="n">
         <v>16.01</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="K70" t="n">
@@ -10461,13 +10473,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45899</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10494,7 +10506,7 @@
       <c r="I71" t="n">
         <v>16.7</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="K71" t="n">
@@ -10507,13 +10519,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10540,7 +10552,7 @@
       <c r="I72" t="n">
         <v>17.16</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="K72" t="n">
@@ -10553,13 +10565,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46171</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46188</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10586,7 +10598,7 @@
       <c r="I73" t="n">
         <v>17.47</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46188</v>
       </c>
       <c r="K73" t="n">
@@ -10599,13 +10611,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46172</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10632,7 +10644,7 @@
       <c r="I74" t="n">
         <v>17.91</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="K74" t="n">
@@ -10669,52 +10681,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39983</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39990</v>
       </c>
       <c r="C2" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40081</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="C3" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40344</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40200</v>
       </c>
       <c r="C4" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40270</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40277</v>
       </c>
       <c r="C5" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40354</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40361</v>
       </c>
       <c r="C6" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40459</v>
       </c>
       <c r="C7" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40564</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="C8" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40641</v>
       </c>
       <c r="C9" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40718</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40723</v>
       </c>
       <c r="C10" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40823</v>
       </c>
       <c r="C11" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40928</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="C12" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40991</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40998</v>
       </c>
       <c r="C13" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41082</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41087</v>
       </c>
       <c r="C14" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41173</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41179</v>
       </c>
       <c r="C15" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41292</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41296</v>
       </c>
       <c r="C16" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41355</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="C17" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41446</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="C18" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41550</v>
       </c>
       <c r="C19" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41656</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41660</v>
       </c>
       <c r="C20" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41719</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41726</v>
       </c>
       <c r="C21" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41810</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41815</v>
       </c>
       <c r="C22" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41901</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41907</v>
       </c>
       <c r="C23" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42020</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42024</v>
       </c>
       <c r="C24" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42083</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42088</v>
       </c>
       <c r="C25" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42174</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42179</v>
       </c>
       <c r="C26" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42265</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="C27" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42384</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42388</v>
       </c>
       <c r="C28" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42454</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="C29" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42545</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42550</v>
       </c>
       <c r="C30" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42636</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42640</v>
       </c>
       <c r="C31" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42748</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="C32" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42818</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42823</v>
       </c>
       <c r="C33" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42909</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42914</v>
       </c>
       <c r="C34" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43000</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43005</v>
       </c>
       <c r="C35" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43122</v>
       </c>
       <c r="C36" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43182</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43187</v>
       </c>
       <c r="C37" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43273</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43278</v>
       </c>
       <c r="C38" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43364</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43369</v>
       </c>
       <c r="C39" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43483</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="C40" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43546</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43551</v>
       </c>
       <c r="C41" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43637</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="C42" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43728</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43734</v>
       </c>
       <c r="C43" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43840</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43851</v>
       </c>
       <c r="C44" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43910</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="C45" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44001</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44006</v>
       </c>
       <c r="C46" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44092</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="C47" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44204</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="C48" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44281</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="C49" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44372</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="C50" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44463</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44468</v>
       </c>
       <c r="C51" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44575</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="C52" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44645</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="C53" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44736</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44741</v>
       </c>
       <c r="C54" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44827</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44832</v>
       </c>
       <c r="C55" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44932</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44943</v>
       </c>
       <c r="C56" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45009</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="C57" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45100</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="C58" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45191</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45196</v>
       </c>
       <c r="C59" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45296</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="C60" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45373</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45378</v>
       </c>
       <c r="C61" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45464</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="C62" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45555</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="C63" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45660</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="C64" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45737</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="C65" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45828</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="C66" t="n">
@@ -12791,10 +12803,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45919</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="C67" t="n">
@@ -12823,10 +12835,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46031</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="C68" t="n">
@@ -12855,10 +12867,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="C69" t="n">
@@ -12887,10 +12899,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46184</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46188</v>
       </c>
       <c r="C70" t="n">
@@ -12919,10 +12931,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="C71" t="n">
@@ -12969,12 +12981,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
